--- a/artfynd/A 7931-2025 artfynd.xlsx
+++ b/artfynd/A 7931-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115774654</v>
+        <v>135497918</v>
       </c>
       <c r="B2" t="n">
-        <v>101326</v>
+        <v>56904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,49 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>208255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blåsippa vid kycklingleden, Liljedal, Vrm</t>
+          <t>Sörvik, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>392227</v>
+        <v>391951</v>
       </c>
       <c r="R2" t="n">
-        <v>6570510</v>
+        <v>6570322</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,12 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,22 +777,131 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Per Flodin</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Per Flodin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115774654</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blåsippa vid kycklingleden, Liljedal, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>392227</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6570510</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Lars Ragnarsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Lars Ragnarsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7931-2025 artfynd.xlsx
+++ b/artfynd/A 7931-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497918</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,8 +912,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115774654</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 7931-2025 artfynd.xlsx
+++ b/artfynd/A 7931-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135497918</v>
       </c>
       <c r="B2" t="n">
-        <v>56904</v>
+        <v>56909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7931-2025 artfynd.xlsx
+++ b/artfynd/A 7931-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115774654</v>
+        <v>135497918</v>
       </c>
       <c r="B2" t="n">
-        <v>101326</v>
+        <v>56909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +691,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>208255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blåsippa vid kycklingleden, Liljedal, Vrm</t>
+          <t>Sörvik, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>392227</v>
+        <v>391951</v>
       </c>
       <c r="R2" t="n">
-        <v>6570510</v>
+        <v>6570322</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +758,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,23 +782,137 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Ragnarsson</t>
+          <t>Per Flodin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Ragnarsson</t>
+          <t>Per Flodin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497918</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115774654</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blåsippa vid kycklingleden, Liljedal, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>392227</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6570510</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115774654</t>
         </is>
@@ -796,6 +921,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7931-2025 artfynd.xlsx
+++ b/artfynd/A 7931-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135497918</v>
       </c>
       <c r="B2" t="n">
-        <v>56909</v>
+        <v>56911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
